--- a/outputs/q3/q3_transport_sorties.xlsx
+++ b/outputs/q3/q3_transport_sorties.xlsx
@@ -517,7 +517,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>U04</t>
+          <t>U03</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -527,28 +527,28 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>O01→S014→O01</t>
+          <t>O01→S006→O01</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>S014:S014-FOD-01,S014-WAT-01</t>
+          <t>S006:S006-MED-01,S006-WAT-03</t>
         </is>
       </c>
       <c r="G2" s="2" t="n">
-        <v>2.716</v>
+        <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>362.716</v>
+        <v>360</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>1993.125811655315</v>
+        <v>1313.47819412363</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>2.369375047807627</v>
+        <v>1.311534858907133</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>0.4734722115983051</v>
+        <v>0.7085478091317483</v>
       </c>
     </row>
     <row r="3">
@@ -559,43 +559,43 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>U01</t>
+          <t>U05</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>A-BAT-05</t>
+          <t>B-BAT-03</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>O01→S002→S004→O01</t>
+          <t>O01→S006→O01</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>S002:S002-MED-01; S004:S004-MED-01,S004-WAT-01</t>
+          <t>S006:S006-WAT-01,S006-WAT-02</t>
         </is>
       </c>
       <c r="G3" s="2" t="n">
-        <v>2277.287</v>
+        <v>1623.052</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>2667.287</v>
+        <v>1983.052</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>4846.380240791447</v>
+        <v>2830.323254843175</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>3.54553377159311</v>
+        <v>1.293521426626286</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0.2121036063126422</v>
+        <v>0.6766196433434286</v>
       </c>
     </row>
     <row r="4">
@@ -606,43 +606,43 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>U03</t>
+          <t>U05</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>A-BAT-04</t>
+          <t>B-BAT-03</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>O01→S014→S011→O01</t>
+          <t>O01→S008→O01</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>S014:S014-MED-01; S011:S011-FOD-01,S011-MED-01</t>
+          <t>S008:S008-FOD-01,S008-MED-01,S008-WAT-01</t>
         </is>
       </c>
       <c r="G4" s="2" t="n">
-        <v>1313.479</v>
+        <v>4869.153</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>1703.479</v>
+        <v>5259.153</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>3970.817647603206</v>
+        <v>6830.984435660332</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>3.184337447129325</v>
+        <v>2.975179434105133</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0.2923694561934833</v>
+        <v>0.2562051414737168</v>
       </c>
     </row>
     <row r="5">
@@ -658,38 +658,38 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>U04</t>
+          <t>U01</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>A-BAT-03</t>
+          <t>A-BAT-05</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>O01→S013→S010→O01</t>
+          <t>O01→S009→O01</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>S013:S013-FOD-01; S010:S010-FOD-01</t>
+          <t>S009:S009-FOD-01,S009-WAT-01</t>
         </is>
       </c>
       <c r="G5" s="2" t="n">
-        <v>1993.126</v>
+        <v>5149.607</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>2353.126</v>
+        <v>5509.607</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>4003.278554011561</v>
+        <v>6838.220231831329</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>2.246688941903741</v>
+        <v>2.331291004787658</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0.5007357906880574</v>
+        <v>0.4819353322694094</v>
       </c>
     </row>
     <row r="6">
@@ -700,43 +700,43 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>U06</t>
+          <t>U08</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>B-BAT-04</t>
+          <t>C-BAT-04</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>O01→S002→O01</t>
+          <t>O01→S001→O01</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>S002:S002-FOD-01</t>
+          <t>S001:S001-HYG-01,S001-MED-01,S001-WAT-03,S001-WAT-04,S001-WAT-06,S001-WAT-07,S001-WAT-08</t>
         </is>
       </c>
       <c r="G6" s="2" t="n">
-        <v>2102.64</v>
+        <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>2432.64</v>
+        <v>510</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>3799.334300098464</v>
+        <v>1560.169077329159</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>2.25598037931713</v>
+        <v>3.037660573722748</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0.4360049051707175</v>
+        <v>0.6202924282846565</v>
       </c>
     </row>
     <row r="7">
@@ -747,43 +747,43 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>U01</t>
+          <t>U06</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>A-BAT-03</t>
+          <t>B-BAT-04</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>O01→S009→S002→O01</t>
+          <t>O01→S008→O01</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>S009:S009-WAT-01; S002:S002-FOD-02</t>
+          <t>S008:S008-HYG-01,S008-WAT-02</t>
         </is>
       </c>
       <c r="G7" s="2" t="n">
-        <v>5152.323</v>
+        <v>3840.745</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>5512.323</v>
+        <v>4200.745</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>7368.13775105334</v>
+        <v>5742.57643566033</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>2.996430446176896</v>
+        <v>2.763405747591705</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0.3341265675162453</v>
+        <v>0.3091485631020738</v>
       </c>
     </row>
     <row r="8">
@@ -794,43 +794,43 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>U05</t>
+          <t>U02</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>B-BAT-03</t>
+          <t>A-BAT-04</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>O01→S007→O01</t>
+          <t>O01→S005→S007→O01</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>S007:S007-HYG-01,S007-WAT-01</t>
+          <t>S005:S005-WAT-01; S007:S007-FOD-01</t>
         </is>
       </c>
       <c r="G8" s="2" t="n">
-        <v>65.366</v>
+        <v>4000.563</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>425.366</v>
+        <v>4360.563</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>1641.641398980425</v>
+        <v>6430.992780442441</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>1.656437870098957</v>
+        <v>3.037738273031008</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0.5858905324752608</v>
+        <v>0.3249470504375539</v>
       </c>
     </row>
     <row r="9">
@@ -841,43 +841,43 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>U03</t>
+          <t>U07</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>A-BAT-05</t>
+          <t>C-BAT-04</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>O01→S006→O01</t>
+          <t>O01→S003→O01</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>S006:S006-MED-01,S006-WAT-03</t>
+          <t>S003:S003-FOD-01,S003-FOD-02,S003-HYG-01,S003-WAT-02,S003-WAT-03,S003-WAT-04</t>
         </is>
       </c>
       <c r="G9" s="2" t="n">
-        <v>0</v>
+        <v>4291.262</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>360</v>
+        <v>4771.262</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>1313.47819412363</v>
+        <v>6727.353349604668</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>1.311534858907133</v>
+        <v>6.149382745183353</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0.7085478091317483</v>
+        <v>0.2313271568520808</v>
       </c>
     </row>
     <row r="10">
@@ -893,38 +893,38 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>U01</t>
+          <t>U02</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>A-BAT-01</t>
+          <t>A-BAT-03</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>O01→S013→S010→O01</t>
+          <t>O01→S014→O01</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>S013:S013-MED-01; S010:S010-MED-01,S010-WAT-01</t>
+          <t>S014:S014-FOD-01,S014-WAT-01</t>
         </is>
       </c>
       <c r="G10" s="2" t="n">
-        <v>36.247</v>
+        <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>426.247</v>
+        <v>360</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>2106.399554011561</v>
+        <v>1990.409811655315</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>2.324208048242129</v>
+        <v>2.369375047807627</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>0.4835093226128603</v>
+        <v>0.4734722115983051</v>
       </c>
     </row>
     <row r="11">
@@ -940,7 +940,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>U04</t>
+          <t>U03</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -950,28 +950,28 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>O01→S009→S005→O01</t>
+          <t>O01→S003→S015→O01</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>S009:S009-MED-01; S005:S005-MED-01,S005-WAT-03</t>
+          <t>S003:S003-MED-01; S015:S015-MED-01,S015-WAT-01</t>
         </is>
       </c>
       <c r="G11" s="2" t="n">
-        <v>4398.57</v>
+        <v>4344.632</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>4788.57</v>
+        <v>4734.632</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>6630.578405143678</v>
+        <v>6947.964416842849</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>2.82130755868744</v>
+        <v>3.360597919140301</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>0.3730427647361244</v>
+        <v>0.2532004624132664</v>
       </c>
     </row>
     <row r="12">
@@ -982,43 +982,43 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>U03</t>
+          <t>U05</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>A-BAT-01</t>
+          <t>B-BAT-02</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>O01→S003→S015→O01</t>
+          <t>O01→S004→O01</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>S003:S003-MED-01; S015:S015-MED-01,S015-WAT-01</t>
+          <t>S004:S004-WAT-02</t>
         </is>
       </c>
       <c r="G12" s="2" t="n">
-        <v>4311.047</v>
+        <v>3007.509</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>4701.047</v>
+        <v>3337.509</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>6914.379416842849</v>
+        <v>4869.152637063279</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>3.360597919140301</v>
+        <v>2.501256146021363</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>0.2532004624132664</v>
+        <v>0.3746859634946593</v>
       </c>
     </row>
     <row r="13">
@@ -1029,43 +1029,43 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>U08</t>
+          <t>U06</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>C-BAT-04</t>
+          <t>B-BAT-01</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>O01→S001→O01</t>
+          <t>O01→S002→O01</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>S001:S001-HYG-01,S001-MED-01,S001-WAT-03,S001-WAT-04,S001-WAT-06,S001-WAT-07,S001-WAT-08</t>
+          <t>S002:S002-FOD-01,S002-FOD-02</t>
         </is>
       </c>
       <c r="G13" s="2" t="n">
-        <v>2072.308</v>
+        <v>2084.05</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>2582.308</v>
+        <v>2444.05</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>3632.477077329159</v>
+        <v>3840.744300098464</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>3.037660573722748</v>
+        <v>2.407208569654083</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>0.6202924282846565</v>
+        <v>0.3981978575864793</v>
       </c>
     </row>
     <row r="14">
@@ -1076,43 +1076,43 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>U06</t>
+          <t>U04</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>B-BAT-02</t>
+          <t>A-BAT-01</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>O01→S007→S015→O01</t>
+          <t>O01→S011→O01</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>S007:S007-WAT-02; S015:S015-FOD-01</t>
+          <t>S011:S011-WAT-01</t>
         </is>
       </c>
       <c r="G14" s="2" t="n">
-        <v>65.366</v>
+        <v>5557.208</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>425.366</v>
+        <v>5887.208</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>2102.639336451001</v>
+        <v>6719.230946657878</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>2.274806876855716</v>
+        <v>1.132481105089803</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>0.4312982807860709</v>
+        <v>0.7483375322022661</v>
       </c>
     </row>
     <row r="15">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>U02</t>
+          <t>U04</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1138,28 +1138,28 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>O01→S011→S007→O01</t>
+          <t>O01→S007→S003→O01</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>S011:S011-WAT-01; S007:S007-FOD-01</t>
+          <t>S007:S007-MED-01; S003:S003-WAT-01</t>
         </is>
       </c>
       <c r="G15" s="2" t="n">
-        <v>5390.738</v>
+        <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>5750.738</v>
+        <v>360</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>7368.139148248344</v>
+        <v>2422.161333486408</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>2.11956291030899</v>
+        <v>2.969258192153887</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>0.5289860199313355</v>
+        <v>0.3401648461880252</v>
       </c>
     </row>
     <row r="16">
@@ -1170,43 +1170,43 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>U06</t>
+          <t>U01</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>B-BAT-02</t>
+          <t>A-BAT-06</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>O01→S008→O01</t>
+          <t>O01→S002→S004→O01</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>S008:S008-FOD-01,S008-MED-01,S008-WAT-01</t>
+          <t>S002:S002-MED-01; S004:S004-MED-01,S004-WAT-01</t>
         </is>
       </c>
       <c r="G16" s="2" t="n">
-        <v>5352.881</v>
+        <v>2229.758</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>5742.881</v>
+        <v>2619.758</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>7314.712435660331</v>
+        <v>4798.851240791447</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>2.975179434105133</v>
+        <v>3.54553377159311</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>0.2562051414737168</v>
+        <v>0.2121036063126422</v>
       </c>
     </row>
     <row r="17">
@@ -1227,33 +1227,33 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>A-BAT-02</t>
+          <t>A-BAT-05</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>O01→S007→S003→O01</t>
+          <t>O01→S013→S010→O01</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>S007:S007-MED-01; S003:S003-WAT-01</t>
+          <t>S013:S013-FOD-01; S010:S010-FOD-01</t>
         </is>
       </c>
       <c r="G17" s="2" t="n">
-        <v>0</v>
+        <v>1990.41</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>360</v>
+        <v>2350.41</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>2422.161333486408</v>
+        <v>4000.56255401156</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>2.969258192153887</v>
+        <v>2.246688941903741</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>0.3401648461880252</v>
+        <v>0.5007357906880574</v>
       </c>
     </row>
     <row r="18">
@@ -1264,43 +1264,43 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>U08</t>
+          <t>U06</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>C-BAT-03</t>
+          <t>B-BAT-01</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>O01→S002→O01</t>
+          <t>O01→S006→O01</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>S002:S002-HYG-01,S002-WAT-01,S002-WAT-02,S002-WAT-03,S002-WAT-04</t>
+          <t>S006:S006-FOD-01,S006-HYG-01</t>
         </is>
       </c>
       <c r="G18" s="2" t="n">
-        <v>30.495</v>
+        <v>5742.577</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>480.495</v>
+        <v>6102.577</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>2072.307384815261</v>
+        <v>6949.848254843174</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>5.999169382284657</v>
+        <v>1.066244988573351</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>0.2501038272144179</v>
+        <v>0.7334387528566623</v>
       </c>
     </row>
     <row r="19">
@@ -1321,33 +1321,33 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>C-BAT-02</t>
+          <t>C-BAT-03</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>O01→S004→S005→O01</t>
+          <t>O01→S005→S004→O01</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>S004:S004-FOD-01,S004-HYG-01,S004-WAT-03; S005:S005-FOD-01,S005-HYG-01,S005-WAT-02</t>
+          <t>S005:S005-FOD-01,S005-HYG-01,S005-WAT-02; S004:S004-FOD-01,S004-HYG-01,S004-WAT-03</t>
         </is>
       </c>
       <c r="G19" s="2" t="n">
-        <v>3642.85</v>
+        <v>3601.983</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>4122.85</v>
+        <v>4081.983</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>6224.590633699631</v>
+        <v>6183.72363369963</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>6.209699801125824</v>
+        <v>5.853031840275717</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>0.223787524859272</v>
+        <v>0.2683710199655354</v>
       </c>
     </row>
     <row r="20">
@@ -1363,7 +1363,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>U05</t>
+          <t>U06</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1373,28 +1373,28 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>O01→S008→O01</t>
+          <t>O01→S007→S015→O01</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>S008:S008-HYG-01,S008-WAT-02</t>
+          <t>S007:S007-WAT-02; S015:S015-FOD-01</t>
         </is>
       </c>
       <c r="G20" s="2" t="n">
-        <v>5443.594</v>
+        <v>46.776</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>5803.594</v>
+        <v>406.776</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>7345.425435660331</v>
+        <v>2084.049336451001</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>2.763405747591705</v>
+        <v>2.274806876855716</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>0.3091485631020738</v>
+        <v>0.4312982807860709</v>
       </c>
     </row>
     <row r="21">
@@ -1405,43 +1405,43 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>U05</t>
+          <t>U03</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>B-BAT-01</t>
+          <t>A-BAT-01</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>O01→S006→O01</t>
+          <t>O01→S014→S011→O01</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>S006:S006-WAT-01,S006-WAT-02</t>
+          <t>S014:S014-MED-01; S011:S011-FOD-01,S011-MED-01</t>
         </is>
       </c>
       <c r="G21" s="2" t="n">
-        <v>1641.642</v>
+        <v>1313.479</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>2001.642</v>
+        <v>1703.479</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>2848.913254843175</v>
+        <v>3970.817647603206</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>1.293521426626286</v>
+        <v>3.184337447129325</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>0.6766196433434286</v>
+        <v>0.2923694561934833</v>
       </c>
     </row>
     <row r="22">
@@ -1457,38 +1457,38 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>U07</t>
+          <t>U08</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>C-BAT-03</t>
+          <t>C-BAT-02</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>O01→S003→O01</t>
+          <t>O01→S002→O01</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>S003:S003-FOD-01,S003-FOD-02,S003-HYG-01,S003-WAT-02,S003-WAT-03,S003-WAT-04</t>
+          <t>S002:S002-HYG-01,S002-WAT-01,S002-WAT-02,S002-WAT-03,S002-WAT-04</t>
         </is>
       </c>
       <c r="G22" s="2" t="n">
-        <v>4530.417</v>
+        <v>1560.17</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>5010.417</v>
+        <v>2010.17</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>6966.508349604669</v>
+        <v>3601.982384815261</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>6.149382745183353</v>
+        <v>5.999169382284657</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>0.2313271568520808</v>
+        <v>0.2501038272144179</v>
       </c>
     </row>
     <row r="23">
@@ -1499,43 +1499,43 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>U06</t>
+          <t>U07</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>B-BAT-01</t>
+          <t>C-BAT-03</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>O01→S006→O01</t>
+          <t>O01→S001→O01</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>S006:S006-FOD-01,S006-HYG-01</t>
+          <t>S001:S001-FOD-01,S001-FOD-02,S001-FOD-03,S001-HYG-02,S001-MED-02,S001-WAT-01,S001-WAT-02,S001-WAT-05</t>
         </is>
       </c>
       <c r="G23" s="2" t="n">
-        <v>4076.107</v>
+        <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>4436.107</v>
+        <v>540</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>5283.378254843174</v>
+        <v>1626.169077329159</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>1.066244988573351</v>
+        <v>2.881041823496958</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>0.7334387528566623</v>
+        <v>0.6398697720628802</v>
       </c>
     </row>
     <row r="24">
@@ -1551,38 +1551,38 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>U02</t>
+          <t>U04</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>A-BAT-06</t>
+          <t>A-BAT-03</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>O01→S005→S009→O01</t>
+          <t>O01→S009→S005→O01</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>S005:S005-WAT-01; S009:S009-FOD-01</t>
+          <t>S009:S009-MED-01; S005:S005-MED-01,S005-WAT-03</t>
         </is>
       </c>
       <c r="G24" s="2" t="n">
-        <v>3177.613</v>
+        <v>3174.897</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>3537.613</v>
+        <v>3564.897</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>5349.621405143677</v>
+        <v>5406.905405143679</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>2.79596015505592</v>
+        <v>2.82130755868744</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>0.3786755210986844</v>
+        <v>0.3730427647361244</v>
       </c>
     </row>
     <row r="25">
@@ -1593,43 +1593,43 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>U07</t>
+          <t>U01</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>C-BAT-02</t>
+          <t>A-BAT-02</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>O01→S001→O01</t>
+          <t>O01→S013→S010→O01</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>S001:S001-FOD-01,S001-FOD-02,S001-FOD-03,S001-HYG-02,S001-MED-02,S001-WAT-01,S001-WAT-02,S001-WAT-05</t>
+          <t>S013:S013-MED-01; S010:S010-MED-01,S010-WAT-01</t>
         </is>
       </c>
       <c r="G25" s="2" t="n">
-        <v>0</v>
+        <v>32.844</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>540</v>
+        <v>422.844</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>1626.169077329159</v>
+        <v>2102.99655401156</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>2.881041823496958</v>
+        <v>2.324208048242129</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>0.6398697720628802</v>
+        <v>0.4835093226128603</v>
       </c>
     </row>
     <row r="26">
@@ -1655,28 +1655,28 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>O01→S012→S013→O01</t>
+          <t>O01→S013→S012→O01</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>S012:S012-FOD-01,S012-MED-01,S012-WAT-01; S013:S013-WAT-01</t>
+          <t>S013:S013-WAT-01; S012:S012-FOD-01,S012-MED-01,S012-WAT-01</t>
         </is>
       </c>
       <c r="G26" s="2" t="n">
-        <v>1626.17</v>
+        <v>1815.961</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>2046.17</v>
+        <v>2235.961</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>3997.328530475288</v>
+        <v>4187.119530475286</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>5.370942002194464</v>
+        <v>5.248275985900307</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>0.328632249725692</v>
+        <v>0.3439655017624617</v>
       </c>
     </row>
     <row r="27">
@@ -1697,33 +1697,33 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>B-BAT-03</t>
+          <t>B-BAT-02</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>O01→S004→O01</t>
+          <t>O01→S007→O01</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>S004:S004-WAT-02</t>
+          <t>S007:S007-HYG-01,S007-WAT-01</t>
         </is>
       </c>
       <c r="G27" s="2" t="n">
-        <v>3026.099</v>
+        <v>46.776</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>3356.099</v>
+        <v>406.776</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>4887.742637063279</v>
+        <v>1623.051398980424</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>2.501256146021363</v>
+        <v>1.656437870098957</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>0.3746859634946593</v>
+        <v>0.5858905324752608</v>
       </c>
     </row>
   </sheetData>
